--- a/proposta_regionais_nova_regional.xlsx
+++ b/proposta_regionais_nova_regional.xlsx
@@ -1345,7 +1345,7 @@
     <t>LUÍS EDUARDO MAGALHÃES</t>
   </si>
   <si>
-    <t>NOVA_REGIONAL</t>
+    <t>NOVA REGIONAL</t>
   </si>
   <si>
     <t>RMS</t>
@@ -4653,7 +4653,7 @@
         <v>9</v>
       </c>
       <c r="F128" t="s">
-        <v>443</v>
+        <v>9</v>
       </c>
       <c r="G128" t="s">
         <v>446</v>
@@ -8839,10 +8839,10 @@
         <v>440</v>
       </c>
       <c r="F310" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G310" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="311" spans="1:7">

--- a/proposta_regionais_nova_regional.xlsx
+++ b/proposta_regionais_nova_regional.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="448">
   <si>
     <t>SENAI</t>
   </si>
@@ -1345,16 +1345,19 @@
     <t>LUÍS EDUARDO MAGALHÃES</t>
   </si>
   <si>
+    <t>CHAPADA (NORTE)</t>
+  </si>
+  <si>
     <t>NOVA REGIONAL</t>
   </si>
   <si>
     <t>RMS</t>
   </si>
   <si>
+    <t>Sim</t>
+  </si>
+  <si>
     <t>Não</t>
-  </si>
-  <si>
-    <t>Sim</t>
   </si>
 </sst>
 </file>
@@ -1755,10 +1758,10 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1781,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1801,7 +1804,7 @@
         <v>440</v>
       </c>
       <c r="F4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G4" t="s">
         <v>446</v>
@@ -1824,7 +1827,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G5" t="s">
         <v>446</v>
@@ -1850,7 +1853,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1873,7 +1876,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1896,7 +1899,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1916,7 +1919,7 @@
         <v>440</v>
       </c>
       <c r="F9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G9" t="s">
         <v>446</v>
@@ -1942,7 +1945,7 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1965,7 +1968,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1988,7 +1991,7 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2011,7 +2014,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2034,7 +2037,7 @@
         <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2057,7 +2060,7 @@
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2077,10 +2080,10 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G16" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2103,7 +2106,7 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2126,7 +2129,7 @@
         <v>7</v>
       </c>
       <c r="G18" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2149,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2169,7 +2172,7 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G20" t="s">
         <v>446</v>
@@ -2195,7 +2198,7 @@
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2218,7 +2221,7 @@
         <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2238,7 +2241,7 @@
         <v>440</v>
       </c>
       <c r="F23" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G23" t="s">
         <v>446</v>
@@ -2264,7 +2267,7 @@
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2287,7 +2290,7 @@
         <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2307,7 +2310,7 @@
         <v>440</v>
       </c>
       <c r="F26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G26" t="s">
         <v>446</v>
@@ -2333,7 +2336,7 @@
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2353,7 +2356,7 @@
         <v>440</v>
       </c>
       <c r="F28" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G28" t="s">
         <v>446</v>
@@ -2379,7 +2382,7 @@
         <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2402,7 +2405,7 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2425,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2448,7 +2451,7 @@
         <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2471,7 +2474,7 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2491,7 +2494,7 @@
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G34" t="s">
         <v>446</v>
@@ -2517,7 +2520,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2537,10 +2540,10 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G36" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2563,7 +2566,7 @@
         <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2586,7 +2589,7 @@
         <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2632,7 +2635,7 @@
         <v>7</v>
       </c>
       <c r="G40" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2655,7 +2658,7 @@
         <v>8</v>
       </c>
       <c r="G41" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2678,7 +2681,7 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2701,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="G43" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2724,7 +2727,7 @@
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2747,7 +2750,7 @@
         <v>12</v>
       </c>
       <c r="G45" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2770,7 +2773,7 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2793,7 +2796,7 @@
         <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2816,7 +2819,7 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2839,7 +2842,7 @@
         <v>7</v>
       </c>
       <c r="G49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2862,7 +2865,7 @@
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2882,10 +2885,10 @@
         <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G51" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2905,10 +2908,10 @@
         <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G52" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2931,7 +2934,7 @@
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2954,7 +2957,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2977,7 +2980,7 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3000,7 +3003,7 @@
         <v>7</v>
       </c>
       <c r="G56" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3023,7 +3026,7 @@
         <v>7</v>
       </c>
       <c r="G57" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3046,7 +3049,7 @@
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3069,7 +3072,7 @@
         <v>10</v>
       </c>
       <c r="G59" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3092,7 +3095,7 @@
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3115,7 +3118,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3138,7 +3141,7 @@
         <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3161,7 +3164,7 @@
         <v>9</v>
       </c>
       <c r="G63" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3184,7 +3187,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3207,7 +3210,7 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3230,7 +3233,7 @@
         <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3253,7 +3256,7 @@
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3276,7 +3279,7 @@
         <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3299,7 +3302,7 @@
         <v>10</v>
       </c>
       <c r="G69" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3322,7 +3325,7 @@
         <v>8</v>
       </c>
       <c r="G70" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3345,7 +3348,7 @@
         <v>10</v>
       </c>
       <c r="G71" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3365,10 +3368,10 @@
         <v>440</v>
       </c>
       <c r="F72" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G72" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3391,7 +3394,7 @@
         <v>10</v>
       </c>
       <c r="G73" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3414,7 +3417,7 @@
         <v>8</v>
       </c>
       <c r="G74" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3437,7 +3440,7 @@
         <v>8</v>
       </c>
       <c r="G75" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3460,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3483,7 +3486,7 @@
         <v>8</v>
       </c>
       <c r="G77" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3506,7 +3509,7 @@
         <v>10</v>
       </c>
       <c r="G78" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3529,7 +3532,7 @@
         <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3549,10 +3552,10 @@
         <v>440</v>
       </c>
       <c r="F80" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G80" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3575,7 +3578,7 @@
         <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3598,7 +3601,7 @@
         <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3621,7 +3624,7 @@
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3644,7 +3647,7 @@
         <v>8</v>
       </c>
       <c r="G84" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3667,7 +3670,7 @@
         <v>9</v>
       </c>
       <c r="G85" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3713,7 +3716,7 @@
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3736,7 +3739,7 @@
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3756,7 +3759,7 @@
         <v>440</v>
       </c>
       <c r="F89" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G89" t="s">
         <v>446</v>
@@ -3782,7 +3785,7 @@
         <v>7</v>
       </c>
       <c r="G90" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3805,7 +3808,7 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3828,7 +3831,7 @@
         <v>9</v>
       </c>
       <c r="G92" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3851,7 +3854,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3871,7 +3874,7 @@
         <v>440</v>
       </c>
       <c r="F94" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G94" t="s">
         <v>446</v>
@@ -3897,7 +3900,7 @@
         <v>12</v>
       </c>
       <c r="G95" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3920,7 +3923,7 @@
         <v>8</v>
       </c>
       <c r="G96" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3943,7 +3946,7 @@
         <v>8</v>
       </c>
       <c r="G97" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3963,7 +3966,7 @@
         <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G98" t="s">
         <v>446</v>
@@ -3986,7 +3989,7 @@
         <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G99" t="s">
         <v>446</v>
@@ -4012,7 +4015,7 @@
         <v>10</v>
       </c>
       <c r="G100" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4035,7 +4038,7 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4058,7 +4061,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4081,7 +4084,7 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4104,7 +4107,7 @@
         <v>9</v>
       </c>
       <c r="G104" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4127,7 +4130,7 @@
         <v>9</v>
       </c>
       <c r="G105" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4147,7 +4150,7 @@
         <v>440</v>
       </c>
       <c r="F106" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G106" t="s">
         <v>446</v>
@@ -4173,7 +4176,7 @@
         <v>12</v>
       </c>
       <c r="G107" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4196,7 +4199,7 @@
         <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4219,7 +4222,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4242,7 +4245,7 @@
         <v>12</v>
       </c>
       <c r="G110" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4265,7 +4268,7 @@
         <v>7</v>
       </c>
       <c r="G111" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4285,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="F112" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G112" t="s">
         <v>446</v>
@@ -4311,7 +4314,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4334,7 +4337,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4357,7 +4360,7 @@
         <v>9</v>
       </c>
       <c r="G115" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4377,7 +4380,7 @@
         <v>9</v>
       </c>
       <c r="F116" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G116" t="s">
         <v>446</v>
@@ -4403,7 +4406,7 @@
         <v>7</v>
       </c>
       <c r="G117" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4426,7 +4429,7 @@
         <v>9</v>
       </c>
       <c r="G118" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4449,7 +4452,7 @@
         <v>8</v>
       </c>
       <c r="G119" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4472,7 +4475,7 @@
         <v>12</v>
       </c>
       <c r="G120" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4492,10 +4495,10 @@
         <v>440</v>
       </c>
       <c r="F121" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G121" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4518,7 +4521,7 @@
         <v>12</v>
       </c>
       <c r="G122" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4541,7 +4544,7 @@
         <v>9</v>
       </c>
       <c r="G123" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4564,7 +4567,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4587,7 +4590,7 @@
         <v>12</v>
       </c>
       <c r="G125" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4607,7 +4610,7 @@
         <v>440</v>
       </c>
       <c r="F126" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G126" t="s">
         <v>446</v>
@@ -4630,7 +4633,7 @@
         <v>440</v>
       </c>
       <c r="F127" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G127" t="s">
         <v>446</v>
@@ -4679,7 +4682,7 @@
         <v>11</v>
       </c>
       <c r="G129" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4699,7 +4702,7 @@
         <v>9</v>
       </c>
       <c r="F130" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G130" t="s">
         <v>446</v>
@@ -4725,7 +4728,7 @@
         <v>7</v>
       </c>
       <c r="G131" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4748,7 +4751,7 @@
         <v>9</v>
       </c>
       <c r="G132" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4771,7 +4774,7 @@
         <v>8</v>
       </c>
       <c r="G133" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4794,7 +4797,7 @@
         <v>12</v>
       </c>
       <c r="G134" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4817,7 +4820,7 @@
         <v>10</v>
       </c>
       <c r="G135" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4840,7 +4843,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4863,7 +4866,7 @@
         <v>10</v>
       </c>
       <c r="G137" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4886,7 +4889,7 @@
         <v>9</v>
       </c>
       <c r="G138" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4909,7 +4912,7 @@
         <v>8</v>
       </c>
       <c r="G139" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4932,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="G140" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4978,7 +4981,7 @@
         <v>9</v>
       </c>
       <c r="G142" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5001,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="G143" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5024,7 +5027,7 @@
         <v>12</v>
       </c>
       <c r="G144" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5047,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="G145" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5067,7 +5070,7 @@
         <v>9</v>
       </c>
       <c r="F146" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G146" t="s">
         <v>446</v>
@@ -5093,7 +5096,7 @@
         <v>9</v>
       </c>
       <c r="G147" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5116,7 +5119,7 @@
         <v>12</v>
       </c>
       <c r="G148" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5139,7 +5142,7 @@
         <v>10</v>
       </c>
       <c r="G149" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5159,10 +5162,10 @@
         <v>12</v>
       </c>
       <c r="F150" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G150" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5185,7 +5188,7 @@
         <v>12</v>
       </c>
       <c r="G151" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5208,7 +5211,7 @@
         <v>8</v>
       </c>
       <c r="G152" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5231,7 +5234,7 @@
         <v>12</v>
       </c>
       <c r="G153" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5254,7 +5257,7 @@
         <v>9</v>
       </c>
       <c r="G154" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5277,7 +5280,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5300,7 +5303,7 @@
         <v>11</v>
       </c>
       <c r="G156" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5343,10 +5346,10 @@
         <v>12</v>
       </c>
       <c r="F158" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G158" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5369,7 +5372,7 @@
         <v>8</v>
       </c>
       <c r="G159" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5392,7 +5395,7 @@
         <v>7</v>
       </c>
       <c r="G160" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5415,7 +5418,7 @@
         <v>9</v>
       </c>
       <c r="G161" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5438,7 +5441,7 @@
         <v>7</v>
       </c>
       <c r="G162" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5461,7 +5464,7 @@
         <v>10</v>
       </c>
       <c r="G163" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5484,7 +5487,7 @@
         <v>12</v>
       </c>
       <c r="G164" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5507,7 +5510,7 @@
         <v>10</v>
       </c>
       <c r="G165" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5527,7 +5530,7 @@
         <v>440</v>
       </c>
       <c r="F166" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G166" t="s">
         <v>446</v>
@@ -5553,7 +5556,7 @@
         <v>9</v>
       </c>
       <c r="G167" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5599,7 +5602,7 @@
         <v>9</v>
       </c>
       <c r="G169" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5622,7 +5625,7 @@
         <v>8</v>
       </c>
       <c r="G170" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5645,7 +5648,7 @@
         <v>9</v>
       </c>
       <c r="G171" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5668,7 +5671,7 @@
         <v>9</v>
       </c>
       <c r="G172" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5688,10 +5691,10 @@
         <v>9</v>
       </c>
       <c r="F173" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G173" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5714,7 +5717,7 @@
         <v>9</v>
       </c>
       <c r="G174" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5737,7 +5740,7 @@
         <v>8</v>
       </c>
       <c r="G175" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5760,7 +5763,7 @@
         <v>11</v>
       </c>
       <c r="G176" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5783,7 +5786,7 @@
         <v>9</v>
       </c>
       <c r="G177" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5806,7 +5809,7 @@
         <v>10</v>
       </c>
       <c r="G178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5829,7 +5832,7 @@
         <v>10</v>
       </c>
       <c r="G179" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5849,10 +5852,10 @@
         <v>9</v>
       </c>
       <c r="F180" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G180" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5875,7 +5878,7 @@
         <v>12</v>
       </c>
       <c r="G181" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5921,7 +5924,7 @@
         <v>11</v>
       </c>
       <c r="G183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5944,7 +5947,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5967,7 +5970,7 @@
         <v>10</v>
       </c>
       <c r="G185" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5990,7 +5993,7 @@
         <v>10</v>
       </c>
       <c r="G186" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6013,7 +6016,7 @@
         <v>11</v>
       </c>
       <c r="G187" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6059,7 +6062,7 @@
         <v>12</v>
       </c>
       <c r="G189" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6079,7 +6082,7 @@
         <v>440</v>
       </c>
       <c r="F190" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G190" t="s">
         <v>446</v>
@@ -6105,7 +6108,7 @@
         <v>11</v>
       </c>
       <c r="G191" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6125,10 +6128,10 @@
         <v>440</v>
       </c>
       <c r="F192" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G192" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6151,7 +6154,7 @@
         <v>10</v>
       </c>
       <c r="G193" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6174,7 +6177,7 @@
         <v>11</v>
       </c>
       <c r="G194" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6197,7 +6200,7 @@
         <v>12</v>
       </c>
       <c r="G195" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6217,7 +6220,7 @@
         <v>9</v>
       </c>
       <c r="F196" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G196" t="s">
         <v>446</v>
@@ -6243,7 +6246,7 @@
         <v>10</v>
       </c>
       <c r="G197" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6266,7 +6269,7 @@
         <v>9</v>
       </c>
       <c r="G198" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6289,7 +6292,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6312,7 +6315,7 @@
         <v>9</v>
       </c>
       <c r="G200" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6335,7 +6338,7 @@
         <v>9</v>
       </c>
       <c r="G201" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6381,7 +6384,7 @@
         <v>12</v>
       </c>
       <c r="G203" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6404,7 +6407,7 @@
         <v>12</v>
       </c>
       <c r="G204" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6427,7 +6430,7 @@
         <v>10</v>
       </c>
       <c r="G205" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6450,7 +6453,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6473,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="G207" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6496,7 +6499,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6519,7 +6522,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6542,7 +6545,7 @@
         <v>9</v>
       </c>
       <c r="G210" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6565,7 +6568,7 @@
         <v>8</v>
       </c>
       <c r="G211" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6588,7 +6591,7 @@
         <v>10</v>
       </c>
       <c r="G212" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6608,7 +6611,7 @@
         <v>440</v>
       </c>
       <c r="F213" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G213" t="s">
         <v>446</v>
@@ -6634,7 +6637,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6654,7 +6657,7 @@
         <v>9</v>
       </c>
       <c r="F215" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G215" t="s">
         <v>446</v>
@@ -6680,7 +6683,7 @@
         <v>9</v>
       </c>
       <c r="G216" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6703,7 +6706,7 @@
         <v>12</v>
       </c>
       <c r="G217" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6726,7 +6729,7 @@
         <v>8</v>
       </c>
       <c r="G218" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6749,7 +6752,7 @@
         <v>8</v>
       </c>
       <c r="G219" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6772,7 +6775,7 @@
         <v>11</v>
       </c>
       <c r="G220" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6795,7 +6798,7 @@
         <v>8</v>
       </c>
       <c r="G221" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6818,7 +6821,7 @@
         <v>10</v>
       </c>
       <c r="G222" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6838,10 +6841,10 @@
         <v>12</v>
       </c>
       <c r="F223" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G223" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6864,7 +6867,7 @@
         <v>9</v>
       </c>
       <c r="G224" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6887,7 +6890,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6910,7 +6913,7 @@
         <v>9</v>
       </c>
       <c r="G226" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6933,7 +6936,7 @@
         <v>11</v>
       </c>
       <c r="G227" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6956,7 +6959,7 @@
         <v>9</v>
       </c>
       <c r="G228" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6979,7 +6982,7 @@
         <v>9</v>
       </c>
       <c r="G229" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7002,7 +7005,7 @@
         <v>9</v>
       </c>
       <c r="G230" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7025,7 +7028,7 @@
         <v>8</v>
       </c>
       <c r="G231" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -7045,10 +7048,10 @@
         <v>440</v>
       </c>
       <c r="F232" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G232" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -7068,10 +7071,10 @@
         <v>9</v>
       </c>
       <c r="F233" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G233" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -7094,7 +7097,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7117,7 +7120,7 @@
         <v>12</v>
       </c>
       <c r="G235" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7140,7 +7143,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7163,7 +7166,7 @@
         <v>9</v>
       </c>
       <c r="G237" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7186,7 +7189,7 @@
         <v>12</v>
       </c>
       <c r="G238" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7209,7 +7212,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7232,7 +7235,7 @@
         <v>8</v>
       </c>
       <c r="G240" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7252,10 +7255,10 @@
         <v>440</v>
       </c>
       <c r="F241" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G241" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7278,7 +7281,7 @@
         <v>12</v>
       </c>
       <c r="G242" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7301,7 +7304,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7324,7 +7327,7 @@
         <v>9</v>
       </c>
       <c r="G244" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7347,7 +7350,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7370,7 +7373,7 @@
         <v>12</v>
       </c>
       <c r="G246" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7393,7 +7396,7 @@
         <v>12</v>
       </c>
       <c r="G247" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7416,7 +7419,7 @@
         <v>7</v>
       </c>
       <c r="G248" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7439,7 +7442,7 @@
         <v>9</v>
       </c>
       <c r="G249" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7462,7 +7465,7 @@
         <v>9</v>
       </c>
       <c r="G250" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7485,7 +7488,7 @@
         <v>10</v>
       </c>
       <c r="G251" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7505,10 +7508,10 @@
         <v>9</v>
       </c>
       <c r="F252" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G252" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7531,7 +7534,7 @@
         <v>10</v>
       </c>
       <c r="G253" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7551,10 +7554,10 @@
         <v>440</v>
       </c>
       <c r="F254" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G254" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7577,7 +7580,7 @@
         <v>7</v>
       </c>
       <c r="G255" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7600,7 +7603,7 @@
         <v>11</v>
       </c>
       <c r="G256" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7623,7 +7626,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7646,7 +7649,7 @@
         <v>9</v>
       </c>
       <c r="G258" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7669,7 +7672,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7692,7 +7695,7 @@
         <v>12</v>
       </c>
       <c r="G260" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7738,7 +7741,7 @@
         <v>7</v>
       </c>
       <c r="G262" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7758,10 +7761,10 @@
         <v>8</v>
       </c>
       <c r="F263" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G263" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7784,7 +7787,7 @@
         <v>12</v>
       </c>
       <c r="G264" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7804,10 +7807,10 @@
         <v>9</v>
       </c>
       <c r="F265" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G265" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7830,7 +7833,7 @@
         <v>11</v>
       </c>
       <c r="G266" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7853,7 +7856,7 @@
         <v>8</v>
       </c>
       <c r="G267" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7876,7 +7879,7 @@
         <v>9</v>
       </c>
       <c r="G268" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7899,7 +7902,7 @@
         <v>9</v>
       </c>
       <c r="G269" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7922,7 +7925,7 @@
         <v>7</v>
       </c>
       <c r="G270" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7945,7 +7948,7 @@
         <v>9</v>
       </c>
       <c r="G271" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7968,7 +7971,7 @@
         <v>9</v>
       </c>
       <c r="G272" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7991,7 +7994,7 @@
         <v>9</v>
       </c>
       <c r="G273" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -8014,7 +8017,7 @@
         <v>10</v>
       </c>
       <c r="G274" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -8037,7 +8040,7 @@
         <v>9</v>
       </c>
       <c r="G275" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -8060,7 +8063,7 @@
         <v>12</v>
       </c>
       <c r="G276" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -8083,7 +8086,7 @@
         <v>9</v>
       </c>
       <c r="G277" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -8129,7 +8132,7 @@
         <v>9</v>
       </c>
       <c r="G279" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -8149,10 +8152,10 @@
         <v>9</v>
       </c>
       <c r="F280" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G280" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -8172,7 +8175,7 @@
         <v>9</v>
       </c>
       <c r="F281" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G281" t="s">
         <v>446</v>
@@ -8198,7 +8201,7 @@
         <v>11</v>
       </c>
       <c r="G282" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -8218,10 +8221,10 @@
         <v>9</v>
       </c>
       <c r="F283" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G283" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8241,7 +8244,7 @@
         <v>9</v>
       </c>
       <c r="F284" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G284" t="s">
         <v>446</v>
@@ -8264,7 +8267,7 @@
         <v>9</v>
       </c>
       <c r="F285" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G285" t="s">
         <v>446</v>
@@ -8290,7 +8293,7 @@
         <v>7</v>
       </c>
       <c r="G286" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8310,7 +8313,7 @@
         <v>440</v>
       </c>
       <c r="F287" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G287" t="s">
         <v>446</v>
@@ -8336,7 +8339,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8359,7 +8362,7 @@
         <v>12</v>
       </c>
       <c r="G289" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8379,10 +8382,10 @@
         <v>9</v>
       </c>
       <c r="F290" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G290" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8405,7 +8408,7 @@
         <v>12</v>
       </c>
       <c r="G291" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8428,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="G292" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8448,7 +8451,7 @@
         <v>9</v>
       </c>
       <c r="F293" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G293" t="s">
         <v>446</v>
@@ -8474,7 +8477,7 @@
         <v>10</v>
       </c>
       <c r="G294" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8497,7 +8500,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8520,7 +8523,7 @@
         <v>9</v>
       </c>
       <c r="G296" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -8540,7 +8543,7 @@
         <v>440</v>
       </c>
       <c r="F297" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G297" t="s">
         <v>446</v>
@@ -8563,7 +8566,7 @@
         <v>9</v>
       </c>
       <c r="F298" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G298" t="s">
         <v>446</v>
@@ -8586,10 +8589,10 @@
         <v>12</v>
       </c>
       <c r="F299" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G299" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -8612,7 +8615,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -8635,7 +8638,7 @@
         <v>12</v>
       </c>
       <c r="G301" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -8658,7 +8661,7 @@
         <v>8</v>
       </c>
       <c r="G302" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -8681,7 +8684,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -8704,7 +8707,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -8727,7 +8730,7 @@
         <v>12</v>
       </c>
       <c r="G305" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -8750,7 +8753,7 @@
         <v>9</v>
       </c>
       <c r="G306" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -8773,7 +8776,7 @@
         <v>9</v>
       </c>
       <c r="G307" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -8796,7 +8799,7 @@
         <v>12</v>
       </c>
       <c r="G308" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -8819,7 +8822,7 @@
         <v>12</v>
       </c>
       <c r="G309" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -8839,7 +8842,7 @@
         <v>440</v>
       </c>
       <c r="F310" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G310" t="s">
         <v>446</v>
@@ -8865,7 +8868,7 @@
         <v>8</v>
       </c>
       <c r="G311" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -8888,7 +8891,7 @@
         <v>11</v>
       </c>
       <c r="G312" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -8911,7 +8914,7 @@
         <v>12</v>
       </c>
       <c r="G313" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -8934,7 +8937,7 @@
         <v>11</v>
       </c>
       <c r="G314" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -8957,7 +8960,7 @@
         <v>8</v>
       </c>
       <c r="G315" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -8980,7 +8983,7 @@
         <v>12</v>
       </c>
       <c r="G316" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -9003,7 +9006,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -9026,7 +9029,7 @@
         <v>9</v>
       </c>
       <c r="G318" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -9049,7 +9052,7 @@
         <v>9</v>
       </c>
       <c r="G319" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -9072,7 +9075,7 @@
         <v>9</v>
       </c>
       <c r="G320" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -9095,7 +9098,7 @@
         <v>9</v>
       </c>
       <c r="G321" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -9118,7 +9121,7 @@
         <v>8</v>
       </c>
       <c r="G322" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -9141,7 +9144,7 @@
         <v>9</v>
       </c>
       <c r="G323" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -9164,7 +9167,7 @@
         <v>7</v>
       </c>
       <c r="G324" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -9187,7 +9190,7 @@
         <v>9</v>
       </c>
       <c r="G325" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -9210,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="G326" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -9230,7 +9233,7 @@
         <v>9</v>
       </c>
       <c r="F327" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G327" t="s">
         <v>446</v>
@@ -9253,7 +9256,7 @@
         <v>9</v>
       </c>
       <c r="F328" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G328" t="s">
         <v>446</v>
@@ -9279,7 +9282,7 @@
         <v>12</v>
       </c>
       <c r="G329" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -9299,10 +9302,10 @@
         <v>12</v>
       </c>
       <c r="F330" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G330" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -9325,7 +9328,7 @@
         <v>12</v>
       </c>
       <c r="G331" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -9348,7 +9351,7 @@
         <v>12</v>
       </c>
       <c r="G332" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -9368,7 +9371,7 @@
         <v>440</v>
       </c>
       <c r="F333" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G333" t="s">
         <v>446</v>
@@ -9394,7 +9397,7 @@
         <v>8</v>
       </c>
       <c r="G334" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -9417,7 +9420,7 @@
         <v>9</v>
       </c>
       <c r="G335" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -9440,7 +9443,7 @@
         <v>9</v>
       </c>
       <c r="G336" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -9460,10 +9463,10 @@
         <v>440</v>
       </c>
       <c r="F337" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G337" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -9486,7 +9489,7 @@
         <v>9</v>
       </c>
       <c r="G338" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="339" spans="1:7">
@@ -9506,7 +9509,7 @@
         <v>9</v>
       </c>
       <c r="F339" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G339" t="s">
         <v>446</v>
@@ -9532,7 +9535,7 @@
         <v>11</v>
       </c>
       <c r="G340" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -9578,7 +9581,7 @@
         <v>9</v>
       </c>
       <c r="G342" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -9601,7 +9604,7 @@
         <v>9</v>
       </c>
       <c r="G343" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -9624,7 +9627,7 @@
         <v>10</v>
       </c>
       <c r="G344" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -9647,7 +9650,7 @@
         <v>7</v>
       </c>
       <c r="G345" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="346" spans="1:7">
@@ -9670,7 +9673,7 @@
         <v>7</v>
       </c>
       <c r="G346" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -9693,7 +9696,7 @@
         <v>9</v>
       </c>
       <c r="G347" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -9716,7 +9719,7 @@
         <v>7</v>
       </c>
       <c r="G348" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -9739,7 +9742,7 @@
         <v>9</v>
       </c>
       <c r="G349" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="350" spans="1:7">
@@ -9762,7 +9765,7 @@
         <v>9</v>
       </c>
       <c r="G350" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -9785,7 +9788,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="352" spans="1:7">
@@ -9808,7 +9811,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -9831,7 +9834,7 @@
         <v>7</v>
       </c>
       <c r="G353" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -9854,7 +9857,7 @@
         <v>9</v>
       </c>
       <c r="G354" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -9877,7 +9880,7 @@
         <v>9</v>
       </c>
       <c r="G355" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -9900,7 +9903,7 @@
         <v>7</v>
       </c>
       <c r="G356" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -9923,7 +9926,7 @@
         <v>9</v>
       </c>
       <c r="G357" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -9943,10 +9946,10 @@
         <v>440</v>
       </c>
       <c r="F358" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G358" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -9969,7 +9972,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -9992,7 +9995,7 @@
         <v>9</v>
       </c>
       <c r="G360" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -10015,7 +10018,7 @@
         <v>10</v>
       </c>
       <c r="G361" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -10038,7 +10041,7 @@
         <v>9</v>
       </c>
       <c r="G362" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -10061,7 +10064,7 @@
         <v>9</v>
       </c>
       <c r="G363" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -10081,10 +10084,10 @@
         <v>440</v>
       </c>
       <c r="F364" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G364" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -10107,7 +10110,7 @@
         <v>9</v>
       </c>
       <c r="G365" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -10127,7 +10130,7 @@
         <v>440</v>
       </c>
       <c r="F366" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G366" t="s">
         <v>446</v>
@@ -10153,7 +10156,7 @@
         <v>9</v>
       </c>
       <c r="G367" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -10176,7 +10179,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -10196,10 +10199,10 @@
         <v>8</v>
       </c>
       <c r="F369" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G369" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -10222,7 +10225,7 @@
         <v>12</v>
       </c>
       <c r="G370" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -10245,7 +10248,7 @@
         <v>8</v>
       </c>
       <c r="G371" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -10268,7 +10271,7 @@
         <v>7</v>
       </c>
       <c r="G372" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -10291,7 +10294,7 @@
         <v>8</v>
       </c>
       <c r="G373" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -10314,7 +10317,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -10337,7 +10340,7 @@
         <v>9</v>
       </c>
       <c r="G375" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="376" spans="1:7">
@@ -10360,7 +10363,7 @@
         <v>9</v>
       </c>
       <c r="G376" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -10383,7 +10386,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -10403,10 +10406,10 @@
         <v>440</v>
       </c>
       <c r="F378" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G378" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="379" spans="1:7">
@@ -10429,7 +10432,7 @@
         <v>7</v>
       </c>
       <c r="G379" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -10449,7 +10452,7 @@
         <v>9</v>
       </c>
       <c r="F380" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G380" t="s">
         <v>446</v>
@@ -10475,7 +10478,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -10495,10 +10498,10 @@
         <v>8</v>
       </c>
       <c r="F382" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G382" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -10521,7 +10524,7 @@
         <v>7</v>
       </c>
       <c r="G383" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -10544,7 +10547,7 @@
         <v>12</v>
       </c>
       <c r="G384" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -10567,7 +10570,7 @@
         <v>12</v>
       </c>
       <c r="G385" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -10590,7 +10593,7 @@
         <v>9</v>
       </c>
       <c r="G386" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -10613,7 +10616,7 @@
         <v>10</v>
       </c>
       <c r="G387" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -10636,7 +10639,7 @@
         <v>9</v>
       </c>
       <c r="G388" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -10659,7 +10662,7 @@
         <v>11</v>
       </c>
       <c r="G389" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -10682,7 +10685,7 @@
         <v>9</v>
       </c>
       <c r="G390" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -10705,7 +10708,7 @@
         <v>9</v>
       </c>
       <c r="G391" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -10728,7 +10731,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -10751,7 +10754,7 @@
         <v>9</v>
       </c>
       <c r="G393" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -10774,7 +10777,7 @@
         <v>12</v>
       </c>
       <c r="G394" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -10797,7 +10800,7 @@
         <v>9</v>
       </c>
       <c r="G395" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -10820,7 +10823,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -10843,7 +10846,7 @@
         <v>9</v>
       </c>
       <c r="G397" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -10866,7 +10869,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -10912,7 +10915,7 @@
         <v>8</v>
       </c>
       <c r="G400" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -10935,7 +10938,7 @@
         <v>8</v>
       </c>
       <c r="G401" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="402" spans="1:7">
@@ -10958,7 +10961,7 @@
         <v>10</v>
       </c>
       <c r="G402" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -10981,7 +10984,7 @@
         <v>12</v>
       </c>
       <c r="G403" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="404" spans="1:7">
@@ -11004,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="G404" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="405" spans="1:7">
@@ -11024,10 +11027,10 @@
         <v>9</v>
       </c>
       <c r="F405" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G405" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -11050,7 +11053,7 @@
         <v>10</v>
       </c>
       <c r="G406" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -11073,7 +11076,7 @@
         <v>9</v>
       </c>
       <c r="G407" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -11096,7 +11099,7 @@
         <v>9</v>
       </c>
       <c r="G408" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="409" spans="1:7">
@@ -11142,7 +11145,7 @@
         <v>8</v>
       </c>
       <c r="G410" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="411" spans="1:7">
@@ -11165,7 +11168,7 @@
         <v>9</v>
       </c>
       <c r="G411" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -11185,10 +11188,10 @@
         <v>440</v>
       </c>
       <c r="F412" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G412" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -11211,7 +11214,7 @@
         <v>11</v>
       </c>
       <c r="G413" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -11234,7 +11237,7 @@
         <v>12</v>
       </c>
       <c r="G414" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -11254,10 +11257,10 @@
         <v>9</v>
       </c>
       <c r="F415" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="G415" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="416" spans="1:7">
@@ -11280,7 +11283,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="417" spans="1:7">
@@ -11303,7 +11306,7 @@
         <v>10</v>
       </c>
       <c r="G417" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="418" spans="1:7">
@@ -11326,7 +11329,7 @@
         <v>8</v>
       </c>
       <c r="G418" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
